--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120412091</v>
+        <v>120412073</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>56535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521022</v>
+        <v>521220</v>
       </c>
       <c r="R2" t="n">
-        <v>6532569</v>
+        <v>6532595</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120412089</v>
+        <v>120412091</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>96888</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521194</v>
+        <v>521022</v>
       </c>
       <c r="R3" t="n">
-        <v>6532572</v>
+        <v>6532569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120412073</v>
+        <v>120412089</v>
       </c>
       <c r="B5" t="n">
-        <v>56535</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,39 +1052,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521220</v>
+        <v>521194</v>
       </c>
       <c r="R5" t="n">
-        <v>6532595</v>
+        <v>6532572</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120412073</v>
+        <v>120412089</v>
       </c>
       <c r="B2" t="n">
-        <v>56535</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521220</v>
+        <v>521194</v>
       </c>
       <c r="R2" t="n">
-        <v>6532595</v>
+        <v>6532572</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120412089</v>
+        <v>120412073</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>56535</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,34 +1048,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521194</v>
+        <v>521220</v>
       </c>
       <c r="R5" t="n">
-        <v>6532572</v>
+        <v>6532595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120412089</v>
+        <v>120412073</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
+        <v>56535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521194</v>
+        <v>521220</v>
       </c>
       <c r="R2" t="n">
-        <v>6532572</v>
+        <v>6532595</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -776,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120412091</v>
+        <v>120412099</v>
       </c>
       <c r="B3" t="n">
-        <v>96888</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521022</v>
+        <v>521194</v>
       </c>
       <c r="R3" t="n">
-        <v>6532569</v>
+        <v>6532572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120412099</v>
+        <v>120412089</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1036,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120412073</v>
+        <v>120412091</v>
       </c>
       <c r="B5" t="n">
-        <v>56535</v>
+        <v>96888</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1055,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521220</v>
+        <v>521022</v>
       </c>
       <c r="R5" t="n">
-        <v>6532595</v>
+        <v>6532569</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120412099</v>
+        <v>120412089</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120412089</v>
+        <v>120412091</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>96888</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,34 +931,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521194</v>
+        <v>521022</v>
       </c>
       <c r="R4" t="n">
-        <v>6532572</v>
+        <v>6532569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120412091</v>
+        <v>120412099</v>
       </c>
       <c r="B5" t="n">
-        <v>96888</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,35 +1052,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521022</v>
+        <v>521194</v>
       </c>
       <c r="R5" t="n">
-        <v>6532569</v>
+        <v>6532572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120412073</v>
+        <v>120412091</v>
       </c>
       <c r="B2" t="n">
-        <v>56535</v>
+        <v>96888</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521220</v>
+        <v>521022</v>
       </c>
       <c r="R2" t="n">
-        <v>6532595</v>
+        <v>6532569</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -919,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120412091</v>
+        <v>120412073</v>
       </c>
       <c r="B4" t="n">
-        <v>96888</v>
+        <v>56535</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +932,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521022</v>
+        <v>521220</v>
       </c>
       <c r="R4" t="n">
-        <v>6532569</v>
+        <v>6532595</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1022,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,126 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122723024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sutterön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520972</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6532506</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>122723024</v>
       </c>
       <c r="B6" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>122723024</v>
       </c>
       <c r="B6" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 25688-2021 artfynd.xlsx
+++ b/artfynd/A 25688-2021 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>122723024</v>
       </c>
       <c r="B6" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
